--- a/docs/primaries-scoring.xlsx
+++ b/docs/primaries-scoring.xlsx
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D4" s="9" t="n">
         <v>3</v>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>4</v>
@@ -3546,7 +3546,7 @@
         <v>2</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>2</v>
@@ -3582,7 +3582,7 @@
         <v>3</v>
       </c>
       <c r="AB16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC16" s="9" t="n">
         <v>1</v>
@@ -4515,7 +4515,7 @@
         <v>2</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N22" s="9" t="n">
         <v>1</v>
@@ -5300,7 +5300,7 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D27" s="9" t="n">
         <v>1</v>
@@ -5752,16 +5752,16 @@
         <v>1</v>
       </c>
       <c r="AS29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT29" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AU29" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV29" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW29" s="9" t="n">
         <v>4</v>
@@ -6564,19 +6564,19 @@
         <v>1</v>
       </c>
       <c r="AR34" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS34" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AT34" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU34" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV34" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW34" s="9" t="n">
         <v>3</v>
@@ -8206,7 +8206,7 @@
         <v>5</v>
       </c>
       <c r="AV44" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW44" s="9" t="n">
         <v>1</v>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D47" s="9" t="n">
         <v>1</v>
@@ -9724,7 +9724,7 @@
         <v>3</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -9858,7 +9858,7 @@
         <v>4</v>
       </c>
       <c r="T4" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U4" s="9" t="n">
         <v>3</v>
@@ -10068,7 +10068,7 @@
         <v>4</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U7" s="9" t="n">
         <v>4</v>
@@ -10686,7 +10686,7 @@
         <v>4</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>3</v>
@@ -11124,7 +11124,7 @@
         <v>3</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -11958,7 +11958,7 @@
         <v>4</v>
       </c>
       <c r="T34" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U34" s="9" t="n">
         <v>3</v>
@@ -12862,7 +12862,7 @@
         <v>2</v>
       </c>
       <c r="R47" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S47" s="9" t="n">
         <v>5</v>

--- a/docs/primaries-scoring.xlsx
+++ b/docs/primaries-scoring.xlsx
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C3" s="9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="9" t="n">
         <v>4</v>
@@ -1397,7 +1397,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="9" t="n">
         <v>3</v>
@@ -1406,19 +1406,19 @@
         <v>2</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" s="9" t="n">
         <v>1</v>
@@ -1442,7 +1442,7 @@
         <v>4</v>
       </c>
       <c r="U3" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V3" s="9" t="n">
         <v>3</v>
@@ -1511,16 +1511,16 @@
         <v>1</v>
       </c>
       <c r="AR3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT3" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV3" s="9" t="n">
         <v>1</v>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>1</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>1</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>1</v>
@@ -2571,7 +2571,7 @@
         <v>5</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R10" s="9" t="n">
         <v>2</v>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>1</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>3</v>
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>1</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>4</v>
@@ -3193,7 +3193,7 @@
         <v>4</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="9" t="n">
         <v>2</v>
@@ -3223,7 +3223,7 @@
         <v>3</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>2</v>
@@ -3283,7 +3283,7 @@
         <v>4</v>
       </c>
       <c r="AK14" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" s="9" t="n">
         <v>2</v>
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>1</v>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>1</v>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>1</v>
@@ -4119,31 +4119,31 @@
         <v>1</v>
       </c>
       <c r="AR19" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS19" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AT19" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU19" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX19" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AY19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA19" s="9" t="n">
         <v>1</v>
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>1</v>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>3</v>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>1</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>1</v>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D32" s="9" t="n">
         <v>1</v>
@@ -6184,7 +6184,7 @@
         <v>1</v>
       </c>
       <c r="Z32" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA32" s="9" t="n">
         <v>2</v>
@@ -6193,7 +6193,7 @@
         <v>1</v>
       </c>
       <c r="AC32" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD32" s="9" t="n">
         <v>1</v>
@@ -6238,16 +6238,16 @@
         <v>1</v>
       </c>
       <c r="AR32" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT32" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV32" s="9" t="n">
         <v>1</v>
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>1</v>
@@ -7093,7 +7093,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>1</v>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="C45" s="9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D45" s="9" t="n">
         <v>1</v>
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D46" s="9" t="n">
         <v>1</v>
